--- a/hw2/results/hw2_results.xlsx
+++ b/hw2/results/hw2_results.xlsx
@@ -14,16 +14,17 @@
     <sheet name="Сравнение моделей" sheetId="5" r:id="rId5"/>
     <sheet name="Фама-Макбет" sheetId="6" r:id="rId6"/>
     <sheet name="Премии за риск" sheetId="7" r:id="rId7"/>
-    <sheet name="Устойчивость" sheetId="8" r:id="rId8"/>
-    <sheet name="Доп. факторы" sheetId="9" r:id="rId9"/>
-    <sheet name="Безрисковая ставка" sheetId="10" r:id="rId10"/>
+    <sheet name="ДЗ1 (15) vs 35" sheetId="8" r:id="rId8"/>
+    <sheet name="Устойчивость" sheetId="9" r:id="rId9"/>
+    <sheet name="Доп. факторы" sheetId="10" r:id="rId10"/>
+    <sheet name="Безрисковая ставка" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="153">
   <si>
     <t>Отрасль</t>
   </si>
@@ -302,6 +303,123 @@
   </si>
   <si>
     <t>Треб. доходность ФФ</t>
+  </si>
+  <si>
+    <t>15 бумаг ДЗ1</t>
+  </si>
+  <si>
+    <t>20 новых бумаг</t>
+  </si>
+  <si>
+    <t>Все 35</t>
+  </si>
+  <si>
+    <t>Акций</t>
+  </si>
+  <si>
+    <t>Диапазон β CAPM</t>
+  </si>
+  <si>
+    <t>Средний R² CAPM</t>
+  </si>
+  <si>
+    <t>Средний R² ФФ</t>
+  </si>
+  <si>
+    <t>Средний скорр. R² CAPM</t>
+  </si>
+  <si>
+    <t>Средний скорр. R² ФФ</t>
+  </si>
+  <si>
+    <t>Средняя |α| CAPM, % год.</t>
+  </si>
+  <si>
+    <t>Средняя |α| ФФ, % год.</t>
+  </si>
+  <si>
+    <t>Значимых α CAPM</t>
+  </si>
+  <si>
+    <t>Значимых α ФФ</t>
+  </si>
+  <si>
+    <t>Значимых нагрузок SMB (+/−)</t>
+  </si>
+  <si>
+    <t>Значимых нагрузок HML (+/−)</t>
+  </si>
+  <si>
+    <t>GRS: акций с полной историей</t>
+  </si>
+  <si>
+    <t>GRS p-value CAPM</t>
+  </si>
+  <si>
+    <t>GRS p-value ФФ</t>
+  </si>
+  <si>
+    <t>Фама–Макбет λ SMB, % год. (t)</t>
+  </si>
+  <si>
+    <t>Фама–Макбет λ HML, % год. (t)</t>
+  </si>
+  <si>
+    <t>Премия ФФ выше CAPM, акций</t>
+  </si>
+  <si>
+    <t>0.55–1.45</t>
+  </si>
+  <si>
+    <t>6 / 1</t>
+  </si>
+  <si>
+    <t>3 / 2</t>
+  </si>
+  <si>
+    <t>27.9 (1.85)</t>
+  </si>
+  <si>
+    <t>-0.0 (-0.00)</t>
+  </si>
+  <si>
+    <t>10 из 15</t>
+  </si>
+  <si>
+    <t>0.64–1.66</t>
+  </si>
+  <si>
+    <t>4 / 2</t>
+  </si>
+  <si>
+    <t>4 / 3</t>
+  </si>
+  <si>
+    <t>-5.9 (-0.30)</t>
+  </si>
+  <si>
+    <t>-12.9 (-1.66)</t>
+  </si>
+  <si>
+    <t>13 из 20</t>
+  </si>
+  <si>
+    <t>0.55–1.66</t>
+  </si>
+  <si>
+    <t>10 / 3</t>
+  </si>
+  <si>
+    <t>7 / 5</t>
+  </si>
+  <si>
+    <t>20.7 (1.54)</t>
+  </si>
+  <si>
+    <t>-7.7 (-0.97)</t>
+  </si>
+  <si>
+    <t>23 из 35</t>
   </si>
   <si>
     <t>Средняя бета рынка</t>
@@ -1579,29 +1697,133 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2">
+        <v>0.3799732501563151</v>
+      </c>
+      <c r="C2">
+        <v>0.3737983691223253</v>
+      </c>
+      <c r="D2">
+        <v>9.812165319865464</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3">
+        <v>0.423257900316813</v>
+      </c>
+      <c r="C3">
+        <v>0.4058162207448757</v>
+      </c>
+      <c r="D3">
+        <v>8.107769382989938</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4">
+        <v>0.4327280854064894</v>
+      </c>
+      <c r="C4">
+        <v>0.4095881960894661</v>
+      </c>
+      <c r="D4">
+        <v>8.336191880259625</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5">
+        <v>0.4414068810270962</v>
+      </c>
+      <c r="C5">
+        <v>0.4126621303982546</v>
+      </c>
+      <c r="D5">
+        <v>8.091465981231558</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="E1" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="F1" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="B2">
         <v>0.7865845733323412</v>
@@ -1621,7 +1843,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="B3">
         <v>0.6985113437547676</v>
@@ -1641,7 +1863,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="B4">
         <v>0.05318912433613446</v>
@@ -5454,12 +5676,285 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4">
+        <v>0.3534820790829845</v>
+      </c>
+      <c r="C4">
+        <v>0.399841628461313</v>
+      </c>
+      <c r="D4">
+        <v>0.3799732501563151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5">
+        <v>0.4026766466226714</v>
+      </c>
+      <c r="C5">
+        <v>0.4386938405874191</v>
+      </c>
+      <c r="D5">
+        <v>0.423257900316813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>0.3473867709842788</v>
+      </c>
+      <c r="C6">
+        <v>0.3936070677258602</v>
+      </c>
+      <c r="D6">
+        <v>0.3737983691223253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7">
+        <v>0.3854471376671634</v>
+      </c>
+      <c r="C7">
+        <v>0.42109303305316</v>
+      </c>
+      <c r="D7">
+        <v>0.4058162207448757</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8">
+        <v>9.328373442017512</v>
+      </c>
+      <c r="C8">
+        <v>10.17500922825143</v>
+      </c>
+      <c r="D8">
+        <v>9.812165319865464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9">
+        <v>7.858762000596529</v>
+      </c>
+      <c r="C9">
+        <v>8.294524919784992</v>
+      </c>
+      <c r="D9">
+        <v>8.107769382989938</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15">
+        <v>0.03519738953911467</v>
+      </c>
+      <c r="C15">
+        <v>0.006754981452790854</v>
+      </c>
+      <c r="D15">
+        <v>0.0153304648192466</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16">
+        <v>0.09558692000989266</v>
+      </c>
+      <c r="C16">
+        <v>0.005370902235205088</v>
+      </c>
+      <c r="D16">
+        <v>0.03712808256614908</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="C1" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="D1" t="s">
         <v>71</v>
@@ -5468,12 +5963,12 @@
         <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
@@ -5493,7 +5988,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C3">
         <v>1.004092964944618</v>
@@ -5510,7 +6005,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -5530,7 +6025,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>1.010240593813291</v>
@@ -5547,7 +6042,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -5567,7 +6062,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="B7" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>1.004752746164001</v>
@@ -5584,7 +6079,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -5604,7 +6099,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="C9">
         <v>0.9780465649841582</v>
@@ -5621,7 +6116,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
@@ -5648,108 +6143,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2">
-        <v>0.3799732501563151</v>
-      </c>
-      <c r="C2">
-        <v>0.3737983691223253</v>
-      </c>
-      <c r="D2">
-        <v>9.812165319865464</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3">
-        <v>0.423257900316813</v>
-      </c>
-      <c r="C3">
-        <v>0.4058162207448757</v>
-      </c>
-      <c r="D3">
-        <v>8.107769382989938</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4">
-        <v>0.4327280854064894</v>
-      </c>
-      <c r="C4">
-        <v>0.4095881960894661</v>
-      </c>
-      <c r="D4">
-        <v>8.336191880259625</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5">
-        <v>0.4414068810270962</v>
-      </c>
-      <c r="C5">
-        <v>0.4126621303982546</v>
-      </c>
-      <c r="D5">
-        <v>8.091465981231558</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>